--- a/c6/downloads/C6/SkyG-Speed-90-BOM.xlsx
+++ b/c6/downloads/C6/SkyG-Speed-90-BOM.xlsx
@@ -2692,7 +2692,7 @@
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Nylon screw M3 x 12</t>
+          <t>Nylon screw M3 x 8</t>
         </is>
       </c>
       <c r="D52" s="7" t="n">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>Nylon PA66 socket or pan head</t>
+          <t>Nylon PA66 pan head</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>M3x12 nylon screw</t>
+          <t>M3x8 nylon screw</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="J52" s="8" t="inlineStr">
         <is>
-          <t>A 16 mm screw here reaches the aileron servo</t>
+          <t>A 12 mm screw here reaches the aileron servo arm (found with the screws modelled in the assembly)</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>1.89</v>
@@ -4074,7 +4074,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>One aircraft (one aircraft with the N0M nose; N0P is an alternative part): 106.9 g, 15.6 h of printing.</t>
+          <t>One aircraft (one aircraft with the N0M nose; N0P is an alternative part): 107.0 g, 15.6 h of printing.</t>
         </is>
       </c>
     </row>

--- a/c6/downloads/C6/SkyG-Speed-90-BOM.xlsx
+++ b/c6/downloads/C6/SkyG-Speed-90-BOM.xlsx
@@ -1438,7 +1438,7 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Nylon screw M3 x 16</t>
+          <t>Nylon countersunk screw M3 x 16</t>
         </is>
       </c>
       <c r="D24" s="7" t="n">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>Nylon PA66 socket or pan head</t>
+          <t>Nylon PA66 countersunk (flat head, DIN 965 / ISO 7046)</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>M3x16 nylon screws</t>
+          <t>M3x16 nylon countersunk screw</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>M2 x 6 screws</t>
+          <t>M2 x 6 countersunk screws (joints)</t>
         </is>
       </c>
       <c r="D26" s="7" t="n">
@@ -1537,17 +1537,17 @@
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>Steel socket/pan head</t>
+          <t>M2 x 6 countersunk (DIN 965), steel</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>M2x6 screws</t>
+          <t>M2x6 countersunk screws</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>Fuselage joints (3 x 2), into internal bosses (4.5 mm thread)</t>
+          <t>Fuselage joints (3 x 2), flush in countersinks in the skin, into internal bosses (4.5 mm thread)</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Nylon screw M3 x 8</t>
+          <t>Nylon countersunk screw M3 x 8</t>
         </is>
       </c>
       <c r="D52" s="7" t="n">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>Nylon PA66 pan head</t>
+          <t>Nylon PA66 countersunk (flat head, DIN 965 / ISO 7046)</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>M3x8 nylon screw</t>
+          <t>M3x8 nylon countersunk screw</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>1.89</v>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>2</v>
@@ -4074,7 +4074,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>One aircraft (one aircraft with the N0M nose; N0P is an alternative part): 107.0 g, 15.6 h of printing.</t>
+          <t>One aircraft (one aircraft with the N0M nose; N0P is an alternative part): 106.7 g, 15.6 h of printing.</t>
         </is>
       </c>
     </row>

--- a/c6/downloads/C6/SkyG-Speed-90-BOM.xlsx
+++ b/c6/downloads/C6/SkyG-Speed-90-BOM.xlsx
@@ -898,24 +898,24 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>65 A single ESC, 4S, BLHeli_32 or AM32 with bidirectional DShot rpm telemetry, &lt;= 33 x 13 x 6 mm</t>
+          <t>4-in-1 70 A AM32 (one channel used): 70 A / 100 A 3 s per channel, 3-8S, bidirectional DShot rpm telemetry, 33 x 43 mm, 13.4 g</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>65A BLHeli_32 / AM32 single ESC (bidirectional DShot)</t>
+          <t>HDZero Halo 4in1 70A ESC AM32</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>Wing bay, on top of the flight controller</t>
+          <t>Wing bay, flat on the flight controller (x 248-291), motor on M1</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
@@ -923,9 +923,9 @@
           <t>Sourced</t>
         </is>
       </c>
-      <c r="J12" s="8" t="inlineStr">
-        <is>
-          <t>C6: rpm telemetry feeds the governor</t>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>https://fpvdronemarket.com/hdzero-halo-4in1-70a-esc-am32 (2026-10-06: the single 65 A ESC was not available in Turkey). Replace the XT60 lead with XT30; only M1 signal, GND and telemetry from the SH1.0 lead; rpm telemetry feeds the governor. Order 1: if the M1 channel fails, move the motor to M2 (no spare ESC needed)</t>
         </is>
       </c>
     </row>
@@ -3377,8 +3377,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/c6/downloads/C6/SkyG-Speed-90-BOM.xlsx
+++ b/c6/downloads/C6/SkyG-Speed-90-BOM.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Printed parts" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Order list (BOM)'!$A$4:$J$66</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Printed parts'!$A$4:$F$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Order list (BOM)'!$A$4:$J$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Printed parts'!$A$4:$F$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>Two rods of ~95 mm: 12 mm horn bent down at the root with a 4 mm outboard pin at its tip; straight run on the hinge axis to y 80; the last 9 mm filed flat (0.3 mm deep, on the side opposite the horn) and epoxied into the D-bore in the aileron's root knuckle. Pushed in from the wing's root face</t>
+          <t>Two rods of ~95 mm: 12 mm horn bent down at the root with a 4 mm outboard pin at its tip; straight run on the hinge axis to y 80; the last 9 mm filed flat (0.3 mm deep, on the side opposite the horn) and epoxied into the D-bore in the aileron's root knuckle. Pushed in from the wing's root face; C6: one 90° bend per rod (horn leg 6 mm from the centreline), printed horn AHR/AHL glued on the leg</t>
         </is>
       </c>
     </row>
@@ -1300,38 +1300,38 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Tail pushrods: wire + micro ball links</t>
+          <t>Pushrods 1.2 mm with Z-bend</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>0.8 mm music wire; M2 threaded solder sleeve; micro ball link M2 with 3 mm brass ball, M1.6 screw/stud + M1.6 nut (buy nuts if the pack has none)</t>
+          <t>1.2 mm steel pushrod with a factory Z-bend, &gt;= 200 mm (cut to length: 2 aileron links about 20 mm, 2 tail pushrods about 75 mm)</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>MP Jet / Hoellein micro ball joint M2, 3 mm ball (pack of 6)</t>
+          <t>Z Tip D1.2mm x 260mm Çelik Pushrod (LXMRC)</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>Tail servo arm (6.7 mm hole, Z-bend) to the horn ball</t>
+          <t>Z-bend in the servo arm (holes drilled to 1.3 mm), 90° L-bend through the printed horn, keeper on the end</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>Z-bend at the servo arm, ball link at the horn (takes the 55 deg skew between the servo and panel axes); link body dimensions are typical: check on receipt</t>
+          <t>Sourced</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>https://www.promodelhobby.com/urun/z-tip-d1-2mm-x-260mm-celik-pushrod-itme-cubugu (C6 simple linkage, 2026-10-06)</t>
         </is>
       </c>
     </row>
@@ -1346,38 +1346,38 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Wheel collar for 2.5 mm shaft + horn arm</t>
+          <t>Pushrod keepers for 1.2 mm wire</t>
         </is>
       </c>
       <c r="D22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E22" s="7" t="n">
-        <v>2</v>
-      </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>Wheel collar for 2.5 mm shaft with set screw (flat filed on the shaft); 1 mm brass horn plate bonded to its inboard face, M1.6 hole 8 mm from the shaft</t>
+          <t>Snap-on L-type pushrod keeper for 1.2 mm wire (pack of 5)</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>2.5 mm wheel collar</t>
+          <t>Pushrod Tutucu d1,2×L11mm (5 adet)</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>Stabilator shafts inside the tail module (horn along the panel normal, link ball on its inboard side)</t>
+          <t>On the protruding L-bend end at each printed horn (2 ailerons, 2 stabilators)</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>Class</t>
+          <t>Sourced</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>File a flat on the shaft under the set screw</t>
+          <t>Promodelhobby, Bağlantı Elemanları (in stock 2026-10-06); unclip the tail pair to remove the tail module</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Z-bend pliers</t>
+          <t>Z-bend pliers, 1.3 mm drill, small flat file</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Forms Z-bends in 0.8 mm music wire</t>
+          <t>Pliers for the 90° L-bends; 1.3 mm drill for the servo-arm holes; flat file for the 0.3 mm flats</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>Tool: Z-bends at the servo arms (aileron links, tail pushrods)</t>
+          <t>Tools: servo arms drilled to 1.3 mm, flats on the stabilator shafts (under the printed horns) and the torque rods</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
@@ -1883,7 +1883,7 @@
       <c r="E34" s="7" t="inlineStr"/>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>22-26 AWG signal, 16 AWG power (battery and motor leads)</t>
+          <t>14 AWG red + black (battery lead and ESC feed, about 0.25 m each colour), 16 AWG black (motor phases, about 0.5 m), 28 AWG in four colours (signals); heat shrink 1.5 / 3 / 4.8 mm</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr"/>
@@ -1897,7 +1897,11 @@
           <t>Class</t>
         </is>
       </c>
-      <c r="J34" s="8" t="inlineStr"/>
+      <c r="J34" s="8" t="inlineStr">
+        <is>
+          <t>Cut lengths per cable: Electrical Integration manual (C6, 2026-10-06)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -3097,37 +3101,37 @@
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Controls</t>
+          <t>Test option</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Music wire 0.8 mm</t>
+          <t>Tail ballast</t>
         </is>
       </c>
       <c r="D61" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>0.8 mm spring steel, &gt;= 200 mm</t>
+          <t>Up to about 3 g</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Music wire 0.8 mm</t>
+          <t>Tungsten putty</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>Aileron links and tail pushrods</t>
+          <t>Floor ballast cup in the tail module (x 400-410), tape over</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
@@ -3137,43 +3141,43 @@
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>Aileron: Z-bend in the 4.3 mm hole of the two-sided KST arm (0.85 mm holes), eye round a 2.0 mm drill on the horn pin; tail: Z-bend in the 6.7 mm hole, M2 solder sleeve at the ball link</t>
+          <t>Only for a heavy micro camera on SkyG Speed 60 (9 g camera: about 2.7 g)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Controls</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Wheel collar 2 mm</t>
+          <t>15T servo arms</t>
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>2 mm bore wheel collar with set screw</t>
+          <t>15T 3.9-4 mm spline arms: two-sided (aileron) with holes at 4.3 mm, one-sided (tail) with a hole at 6.7 mm; C6: holes drilled to 1.3 mm for the 1.2 mm Z-bends</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>2 mm wheel collar</t>
+          <t>Arms supplied with the ES9052MD (drill a 0.85 mm hole at the radius if missing) or a KST X06 arm set</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>On each torque-rod horn pin, outboard of the link eye</t>
+          <t>Aileron servo: two-sided arm; tail servos: one-sided arms</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
@@ -3183,43 +3187,43 @@
       </c>
       <c r="J62" s="8" t="inlineStr">
         <is>
-          <t>Keeps the link eye on the pin</t>
+          <t>Usually supplied with the servos</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Test option</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Tail ballast</t>
+          <t>u.FL extension 1.13 mm, about 250 mm</t>
         </is>
       </c>
       <c r="D63" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Up to about 3 g</t>
+          <t>IPEX / u.FL male to u.FL female 1.13 mm coax, 200-300 mm</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>Tungsten putty</t>
+          <t>u.FL IPEX extension cable 1.13 mm</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>Floor ballast cup in the tail module (x 400-410), tape over</t>
+          <t>RP1 V2 receiver to the dipole in the fin (W07), u.FL joint at the tail joint</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
@@ -3229,43 +3233,43 @@
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>Only for a heavy micro camera on SkyG Speed 60 (9 g camera: about 2.7 g)</t>
+          <t>C6: ELRS dipole in the fin (2026-10-06)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>Controls</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>15T servo arms</t>
+          <t>Dupont housings + crimps (1-pin, 4-pin)</t>
         </is>
       </c>
       <c r="D64" s="7" t="n">
         <v>1</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>15T 3.9-4 mm spline arms with 0.85 mm holes at 4.3 mm (two-sided, aileron) and 6.7 mm (one-sided, tail)</t>
+          <t>2.54 mm Dupont female housings with crimp terminals</t>
         </is>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>Arms supplied with the ES9052MD (drill a 0.85 mm hole at the radius if missing) or a KST X06 arm set</t>
+          <t>Dupont connector kit 2.54 mm</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>Aileron servo: two-sided arm; tail servos: one-sided arms</t>
+          <t>ESC signal and GND on S1 (2 x 1-pin), receiver lead on the FC receiver header (4-pin)</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
@@ -3273,113 +3277,18 @@
           <t>Class</t>
         </is>
       </c>
-      <c r="J64" s="8" t="inlineStr">
-        <is>
-          <t>Usually supplied with the servos</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>Controls</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>Brass sheet 1 mm</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>1 mm brass, about 4 x 12 mm per horn</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="inlineStr">
-        <is>
-          <t>K&amp;S brass sheet 1 mm</t>
-        </is>
-      </c>
-      <c r="H65" s="5" t="inlineStr">
-        <is>
-          <t>Tail horn plates (bonded to the wheel collars, M1.6 hole at 8 mm)</t>
-        </is>
-      </c>
-      <c r="I65" s="4" t="inlineStr">
-        <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="J65" s="5" t="inlineStr">
-        <is>
-          <t>Solder or epoxy to the collar face</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="7" t="n">
-        <v>67</v>
-      </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>Hardware</t>
-        </is>
-      </c>
-      <c r="C66" s="8" t="inlineStr">
-        <is>
-          <t>M1.6 nuts</t>
-        </is>
-      </c>
-      <c r="D66" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E66" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F66" s="8" t="inlineStr">
-        <is>
-          <t>M1.6 hex nuts, steel</t>
-        </is>
-      </c>
-      <c r="G66" s="8" t="inlineStr">
-        <is>
-          <t>M1.6 nut</t>
-        </is>
-      </c>
-      <c r="H66" s="8" t="inlineStr">
-        <is>
-          <t>Tail horn ball studs (outboard of the horn plate)</t>
-        </is>
-      </c>
-      <c r="I66" s="7" t="inlineStr">
-        <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="J66" s="8" t="inlineStr">
-        <is>
-          <t>Thread-lock</t>
-        </is>
-      </c>
+      <c r="J64" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J66"/>
+  <autoFilter ref="A4:J64"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3391,7 +3300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3749,7 +3658,7 @@
         <v>20.6</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>2</v>
@@ -3879,7 +3788,7 @@
         <v>16.3</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>1</v>
@@ -4032,10 +3941,10 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>2</v>
@@ -4072,29 +3981,133 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>AHR-aileron-horn-right</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>PLA</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>40 %</t>
+        </is>
+      </c>
+    </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>One aircraft (one aircraft with the N0M nose; N0P is an alternative part): 106.7 g, 15.6 h of printing.</t>
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>AHL-aileron-horn-left</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>PLA</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>40 %</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>THR-tail-horn-right</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>PLA</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>40 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>THL-tail-horn-left</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>PLA</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>40 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>One aircraft (one aircraft with the N0M nose; N0P is an alternative part): 107.5 g, 15.7 h of printing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Print every part with supports OFF, in the orientation of the user manual (all parts pass the print audit, design/DFAM-RULES.md).</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Only one camera nose is needed; the other noses (and their dome ring or VTX shelf) are options.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F28"/>
+  <autoFilter ref="A4:F32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/c6/downloads/C6/SkyG-Speed-90-BOM.xlsx
+++ b/c6/downloads/C6/SkyG-Speed-90-BOM.xlsx
@@ -3372,7 +3372,7 @@
         <v>6</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>2</v>

--- a/c6/downloads/C6/SkyG-Speed-90-BOM.xlsx
+++ b/c6/downloads/C6/SkyG-Speed-90-BOM.xlsx
@@ -1321,7 +1321,7 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>Z-bend in the servo arm (holes drilled to 1.3 mm), 90° L-bend through the printed horn, keeper on the end</t>
+          <t>Z-bend in the servo arm (hole drilled 1.1 mm, reamed to 1.2 mm), 90° L-bend through the printed horn (reamed the same), keeper on the end</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Z-bend pliers, 1.3 mm drill, small flat file</t>
+          <t>Z-bend pliers, 1.1 mm drill, 1.2 mm drill (as a hand reamer), small flat file</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Pliers for the 90° L-bends; 1.3 mm drill for the servo-arm holes; flat file for the 0.3 mm flats</t>
+          <t>Pliers for the 90° L-bends; servo-arm and horn holes drilled 1.1 mm then reamed by hand with the 1.2 mm bit (zero play); flat file for the 0.3 mm flats</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>Tools: servo arms drilled to 1.3 mm, flats on the stabilator shafts (under the printed horns) and the torque rods</t>
+          <t>Tools: servo-arm and horn holes reamed to 1.2 mm, flats on the stabilator shafts (under the printed horns) and the torque rods</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Nylon countersunk screw M3 x 8</t>
+          <t>Nylon countersunk screw M3 x 12</t>
         </is>
       </c>
       <c r="D52" s="7" t="n">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>M3x8 nylon countersunk screw</t>
+          <t>M3x12 nylon countersunk screw</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>Wing mount, rear screw (x = wing LE + 84)</t>
+          <t>Wing mount, rear screw (x = wing LE + 58, ahead of the aileron horns)</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="J52" s="8" t="inlineStr">
         <is>
-          <t>A 12 mm screw here reaches the aileron servo arm (found with the screws modelled in the assembly)</t>
+          <t>2026-10-07: moved from LE + 84 so its nut bridge can grow from the side walls on a pointed-arch lead-in (DFAM A2l; at LE + 84 the lead-in ran through the aileron horns' sweep). The wing is 7.4 mm thick there: 12 mm reaches through the nut</t>
         </is>
       </c>
     </row>
@@ -3167,7 +3167,7 @@
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>15T 3.9-4 mm spline arms: two-sided (aileron) with holes at 4.3 mm, one-sided (tail) with a hole at 6.7 mm; C6: holes drilled to 1.3 mm for the 1.2 mm Z-bends</t>
+          <t>15T 3.9-4 mm spline arms: two-sided (aileron) with holes at 4.3 mm, one-sided (tail) with a hole at 6.7 mm; C6: holes drilled 1.1 mm and reamed to 1.2 mm for the 1.2 mm Z-bends (no play)</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
@@ -3369,17 +3369,17 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>0 %</t>
+          <t>30 %</t>
         </is>
       </c>
     </row>
@@ -3395,17 +3395,17 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>0 %</t>
+          <t>30 %</t>
         </is>
       </c>
     </row>
@@ -3421,17 +3421,17 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>0 %</t>
+          <t>30 %</t>
         </is>
       </c>
     </row>
@@ -3447,17 +3447,17 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>0 %</t>
+          <t>30 %</t>
         </is>
       </c>
     </row>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>15 %</t>
+          <t>30 %</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>15 %</t>
+          <t>30 %</t>
         </is>
       </c>
     </row>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>15 %</t>
+          <t>30 %</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>15 %</t>
+          <t>30 %</t>
         </is>
       </c>
     </row>
@@ -3577,17 +3577,17 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>0 %</t>
+          <t>30 %</t>
         </is>
       </c>
     </row>
@@ -3603,17 +3603,17 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>0 %</t>
+          <t>30 %</t>
         </is>
       </c>
     </row>
@@ -3629,17 +3629,17 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>17.2</v>
+        <v>17.4</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>0 %</t>
+          <t>30 %</t>
         </is>
       </c>
     </row>
@@ -3655,17 +3655,17 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>20.6</v>
+        <v>21.7</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>0 %</t>
+          <t>30 %</t>
         </is>
       </c>
     </row>
@@ -3681,17 +3681,17 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.99</v>
+        <v>1.04</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>0 %</t>
+          <t>30 %</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>0 %</t>
+          <t>30 %</t>
         </is>
       </c>
     </row>
@@ -3733,17 +3733,17 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>15 %</t>
+          <t>30 %</t>
         </is>
       </c>
     </row>
@@ -3759,10 +3759,10 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>15.4</v>
+        <v>16.3</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>1</v>
@@ -3788,7 +3788,7 @@
         <v>16.3</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>1</v>
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>1</v>
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>1</v>
@@ -3941,17 +3941,17 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>15 %</t>
+          <t>30 %</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>One aircraft (one aircraft with the N0M nose; N0P is an alternative part): 107.5 g, 15.7 h of printing.</t>
+          <t>One aircraft (one aircraft with the N0M nose; N0P is an alternative part): 109.5 g, 15.9 h of printing.</t>
         </is>
       </c>
     </row>
